--- a/画面設計/【画面設計】02_料理検索画面.xlsx
+++ b/画面設計/【画面設計】02_料理検索画面.xlsx
@@ -12,14 +12,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="N0JsAZwBs8AGOA+MZJFhBVF1ZkNlLXIx5Y0SUwI05pA="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="rng7HIqQMOGUPXUUTrN1nK69NHus+0FcVdFL/rmI5LU="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="124">
   <si>
     <t>アプリ課題(2025）</t>
   </si>
@@ -79,9 +79,6 @@
   </si>
   <si>
     <t>（詳細検索時）</t>
-  </si>
-  <si>
-    <t>名称は全て１箇所で管理</t>
   </si>
   <si>
     <t>2.【機能概要】</t>
@@ -153,6 +150,9 @@
   </si>
   <si>
     <t>参照：【画面設計】01_メニュー画面.xlsx</t>
+  </si>
+  <si>
+    <t>（検索条件）</t>
   </si>
   <si>
     <t>数値のみ</t>
@@ -1156,6 +1156,57 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3781425" cy="11325225"/>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="2" name="Shape 2" title="図形描画"/>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="152400" y="152400"/>
+          <a:ext cx="2409825" cy="7258050"/>
+          <a:chOff x="152400" y="152400"/>
+          <a:chExt cx="2409825" cy="7258050"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="3" name="Shape 3"/>
+          <xdr:cNvPicPr preferRelativeResize="0"/>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip r:embed="rId1">
+            <a:alphaModFix/>
+          </a:blip>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="152400" y="152400"/>
+            <a:ext cx="2409825" cy="7258050"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>590550</xdr:colOff>
       <xdr:row>8</xdr:row>
@@ -1164,11 +1215,11 @@
     <xdr:ext cx="5753100" cy="5629275"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="画像"/>
+        <xdr:cNvPr id="0" name="image1.png" title="画像"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,35 +1243,7 @@
     <xdr:ext cx="5753100" cy="5295900"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="画像"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="12677775" cy="11544300"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.png" title="画像"/>
+        <xdr:cNvPr id="0" name="image2.png" title="画像"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1270,7 +1293,7 @@
       </xdr:grpSpPr>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="3" name="Shape 3"/>
+          <xdr:cNvPr id="4" name="Shape 4"/>
           <xdr:cNvPicPr preferRelativeResize="0"/>
         </xdr:nvPicPr>
         <xdr:blipFill>
@@ -1321,7 +1344,7 @@
       </xdr:grpSpPr>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="4" name="Shape 4"/>
+          <xdr:cNvPr id="5" name="Shape 5"/>
           <xdr:cNvPicPr preferRelativeResize="0"/>
         </xdr:nvPicPr>
         <xdr:blipFill>
@@ -1372,7 +1395,7 @@
       </xdr:grpSpPr>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="5" name="Shape 5"/>
+          <xdr:cNvPr id="6" name="Shape 6"/>
           <xdr:cNvPicPr preferRelativeResize="0"/>
         </xdr:nvPicPr>
         <xdr:blipFill>
@@ -1410,7 +1433,7 @@
     <xdr:ext cx="3762375" cy="457200"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg" title="画像"/>
+        <xdr:cNvPr id="0" name="image3.jpg" title="画像"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4165,9 +4188,7 @@
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
       <c r="O45" s="6"/>
-      <c r="P45" s="28" t="s">
-        <v>20</v>
-      </c>
+      <c r="P45" s="28"/>
       <c r="Q45" s="6"/>
       <c r="R45" s="6"/>
       <c r="S45" s="6"/>
@@ -4658,7 +4679,7 @@
     <row r="63" ht="16.5" customHeight="1">
       <c r="A63" s="6"/>
       <c r="B63" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
@@ -4688,7 +4709,7 @@
     <row r="64" ht="16.5" customHeight="1">
       <c r="A64" s="6"/>
       <c r="B64" s="29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -4797,7 +4818,7 @@
     <row r="68" ht="16.5" customHeight="1">
       <c r="A68" s="6"/>
       <c r="B68" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
@@ -4827,13 +4848,13 @@
     <row r="69" ht="16.5" customHeight="1">
       <c r="A69" s="6"/>
       <c r="B69" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="C69" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="C69" s="32" t="s">
+      <c r="D69" s="32" t="s">
         <v>25</v>
-      </c>
-      <c r="D69" s="32" t="s">
-        <v>26</v>
       </c>
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
@@ -4917,7 +4938,7 @@
     <row r="72" ht="16.5" customHeight="1">
       <c r="A72" s="6"/>
       <c r="B72" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="6"/>
@@ -4947,10 +4968,10 @@
     <row r="73" ht="16.5" customHeight="1">
       <c r="A73" s="6"/>
       <c r="B73" s="32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C73" s="36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D73" s="20"/>
       <c r="E73" s="6"/>
@@ -4979,10 +5000,10 @@
     <row r="74" ht="34.5" customHeight="1">
       <c r="A74" s="6"/>
       <c r="B74" s="37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C74" s="38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D74" s="20"/>
       <c r="E74" s="6"/>
@@ -5011,10 +5032,10 @@
     <row r="75" ht="39.75" customHeight="1">
       <c r="A75" s="6"/>
       <c r="B75" s="37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C75" s="38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D75" s="20"/>
       <c r="E75" s="6"/>
@@ -5043,10 +5064,10 @@
     <row r="76" ht="39.0" customHeight="1">
       <c r="A76" s="6"/>
       <c r="B76" s="37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C76" s="39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D76" s="20"/>
       <c r="E76" s="6"/>
@@ -5103,14 +5124,14 @@
     <row r="78" ht="16.5" customHeight="1">
       <c r="A78" s="6"/>
       <c r="B78" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="6"/>
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
       <c r="G78" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H78" s="6"/>
       <c r="I78" s="6"/>
@@ -5135,30 +5156,30 @@
     <row r="79" ht="16.5" customHeight="1">
       <c r="A79" s="6"/>
       <c r="B79" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C79" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="C79" s="32" t="s">
+      <c r="D79" s="32" t="s">
         <v>38</v>
-      </c>
-      <c r="D79" s="32" t="s">
-        <v>39</v>
       </c>
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
       <c r="G79" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="H79" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="H79" s="32" t="s">
-        <v>41</v>
+      <c r="I79" s="32" t="s">
+        <v>24</v>
       </c>
-      <c r="I79" s="32" t="s">
+      <c r="J79" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="J79" s="32" t="s">
-        <v>26</v>
-      </c>
       <c r="K79" s="32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L79" s="6"/>
       <c r="M79" s="6"/>
@@ -5179,10 +5200,10 @@
     <row r="80" ht="21.0" customHeight="1">
       <c r="A80" s="40"/>
       <c r="B80" s="41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C80" s="42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D80" s="9"/>
       <c r="E80" s="24"/>
@@ -5213,9 +5234,7 @@
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
       <c r="D81" s="6"/>
-      <c r="E81" s="44" t="s">
-        <v>44</v>
-      </c>
+      <c r="E81" s="44"/>
       <c r="F81" s="6"/>
       <c r="G81" s="6"/>
       <c r="H81" s="6"/>
@@ -5240,34 +5259,20 @@
     </row>
     <row r="82" ht="16.5" customHeight="1">
       <c r="A82" s="6"/>
-      <c r="B82" s="32" t="s">
-        <v>37</v>
+      <c r="B82" s="27" t="s">
+        <v>43</v>
       </c>
-      <c r="C82" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="D82" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="E82" s="45" t="s">
-        <v>45</v>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="44" t="s">
+        <v>44</v>
       </c>
       <c r="F82" s="6"/>
-      <c r="G82" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="H82" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="I82" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="J82" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="K82" s="32" t="s">
-        <v>39</v>
-      </c>
+      <c r="G82" s="6"/>
+      <c r="H82" s="6"/>
+      <c r="I82" s="6"/>
+      <c r="J82" s="6"/>
+      <c r="K82" s="6"/>
       <c r="L82" s="6"/>
       <c r="M82" s="6"/>
       <c r="N82" s="6"/>
@@ -5284,52 +5289,64 @@
       <c r="Y82" s="6"/>
       <c r="Z82" s="6"/>
     </row>
-    <row r="83" ht="21.0" customHeight="1">
-      <c r="A83" s="40"/>
-      <c r="B83" s="46" t="s">
+    <row r="83" ht="16.5" customHeight="1">
+      <c r="A83" s="6"/>
+      <c r="B83" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C83" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="D83" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="E83" s="45" t="s">
+        <v>45</v>
+      </c>
+      <c r="F83" s="6"/>
+      <c r="G83" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="H83" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="I83" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="J83" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="K83" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="L83" s="6"/>
+      <c r="M83" s="6"/>
+      <c r="N83" s="6"/>
+      <c r="O83" s="6"/>
+      <c r="P83" s="6"/>
+      <c r="Q83" s="6"/>
+      <c r="R83" s="6"/>
+      <c r="S83" s="6"/>
+      <c r="T83" s="6"/>
+      <c r="U83" s="6"/>
+      <c r="V83" s="6"/>
+      <c r="W83" s="6"/>
+      <c r="X83" s="6"/>
+      <c r="Y83" s="6"/>
+      <c r="Z83" s="6"/>
+    </row>
+    <row r="84" ht="21.0" customHeight="1">
+      <c r="A84" s="40"/>
+      <c r="B84" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="C83" s="41" t="s">
+      <c r="C84" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="D83" s="47" t="s">
+      <c r="D84" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="E83" s="48"/>
-      <c r="F83" s="40"/>
-      <c r="G83" s="49"/>
-      <c r="H83" s="49"/>
-      <c r="I83" s="49"/>
-      <c r="J83" s="49"/>
-      <c r="K83" s="49"/>
-      <c r="L83" s="24"/>
-      <c r="M83" s="24"/>
-      <c r="N83" s="24"/>
-      <c r="O83" s="24"/>
-      <c r="P83" s="24"/>
-      <c r="Q83" s="24"/>
-      <c r="R83" s="24"/>
-      <c r="S83" s="24"/>
-      <c r="T83" s="24"/>
-      <c r="U83" s="24"/>
-      <c r="V83" s="24"/>
-      <c r="W83" s="24"/>
-      <c r="X83" s="24"/>
-      <c r="Y83" s="24"/>
-      <c r="Z83" s="24"/>
-    </row>
-    <row r="84" ht="37.5" customHeight="1">
-      <c r="A84" s="40"/>
-      <c r="B84" s="50" t="s">
-        <v>49</v>
-      </c>
-      <c r="C84" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="D84" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="E84" s="51"/>
+      <c r="E84" s="48"/>
       <c r="F84" s="40"/>
       <c r="G84" s="49"/>
       <c r="H84" s="49"/>
@@ -5352,18 +5369,18 @@
       <c r="Y84" s="24"/>
       <c r="Z84" s="24"/>
     </row>
-    <row r="85" ht="23.25" customHeight="1">
+    <row r="85" ht="37.5" customHeight="1">
       <c r="A85" s="40"/>
-      <c r="B85" s="52" t="s">
-        <v>51</v>
+      <c r="B85" s="50" t="s">
+        <v>49</v>
       </c>
-      <c r="C85" s="53" t="s">
-        <v>52</v>
+      <c r="C85" s="41" t="s">
+        <v>50</v>
       </c>
-      <c r="D85" s="54" t="s">
-        <v>53</v>
+      <c r="D85" s="47" t="s">
+        <v>30</v>
       </c>
-      <c r="E85" s="55"/>
+      <c r="E85" s="51"/>
       <c r="F85" s="40"/>
       <c r="G85" s="49"/>
       <c r="H85" s="49"/>
@@ -5386,14 +5403,18 @@
       <c r="Y85" s="24"/>
       <c r="Z85" s="24"/>
     </row>
-    <row r="86" ht="18.75" customHeight="1">
+    <row r="86" ht="23.25" customHeight="1">
       <c r="A86" s="40"/>
-      <c r="B86" s="56" t="s">
-        <v>54</v>
+      <c r="B86" s="52" t="s">
+        <v>51</v>
       </c>
-      <c r="C86" s="19"/>
-      <c r="D86" s="19"/>
-      <c r="E86" s="20"/>
+      <c r="C86" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="D86" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="E86" s="55"/>
       <c r="F86" s="40"/>
       <c r="G86" s="49"/>
       <c r="H86" s="49"/>
@@ -5416,18 +5437,14 @@
       <c r="Y86" s="24"/>
       <c r="Z86" s="24"/>
     </row>
-    <row r="87" ht="24.75" customHeight="1">
+    <row r="87" ht="18.75" customHeight="1">
       <c r="A87" s="40"/>
-      <c r="B87" s="50" t="s">
-        <v>55</v>
+      <c r="B87" s="56" t="s">
+        <v>54</v>
       </c>
-      <c r="C87" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="D87" s="47" t="s">
-        <v>57</v>
-      </c>
-      <c r="E87" s="57"/>
+      <c r="C87" s="19"/>
+      <c r="D87" s="19"/>
+      <c r="E87" s="20"/>
       <c r="F87" s="40"/>
       <c r="G87" s="49"/>
       <c r="H87" s="49"/>
@@ -5450,16 +5467,16 @@
       <c r="Y87" s="24"/>
       <c r="Z87" s="24"/>
     </row>
-    <row r="88" ht="21.0" customHeight="1">
+    <row r="88" ht="24.75" customHeight="1">
       <c r="A88" s="40"/>
       <c r="B88" s="50" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C88" s="50" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
-      <c r="D88" s="58" t="s">
-        <v>59</v>
+      <c r="D88" s="47" t="s">
+        <v>57</v>
       </c>
       <c r="E88" s="57"/>
       <c r="F88" s="40"/>
@@ -5486,16 +5503,16 @@
     </row>
     <row r="89" ht="21.0" customHeight="1">
       <c r="A89" s="40"/>
-      <c r="B89" s="59" t="s">
-        <v>60</v>
+      <c r="B89" s="50" t="s">
+        <v>58</v>
       </c>
-      <c r="C89" s="60" t="s">
-        <v>52</v>
+      <c r="C89" s="50" t="s">
+        <v>58</v>
       </c>
-      <c r="D89" s="61" t="s">
-        <v>61</v>
+      <c r="D89" s="58" t="s">
+        <v>59</v>
       </c>
-      <c r="E89" s="62"/>
+      <c r="E89" s="57"/>
       <c r="F89" s="40"/>
       <c r="G89" s="49"/>
       <c r="H89" s="49"/>
@@ -5518,14 +5535,18 @@
       <c r="Y89" s="24"/>
       <c r="Z89" s="24"/>
     </row>
-    <row r="90" ht="18.75" customHeight="1">
+    <row r="90" ht="21.0" customHeight="1">
       <c r="A90" s="40"/>
-      <c r="B90" s="63" t="s">
-        <v>62</v>
+      <c r="B90" s="59" t="s">
+        <v>60</v>
       </c>
-      <c r="C90" s="19"/>
-      <c r="D90" s="19"/>
-      <c r="E90" s="20"/>
+      <c r="C90" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="D90" s="61" t="s">
+        <v>61</v>
+      </c>
+      <c r="E90" s="62"/>
       <c r="F90" s="40"/>
       <c r="G90" s="49"/>
       <c r="H90" s="49"/>
@@ -5548,18 +5569,14 @@
       <c r="Y90" s="24"/>
       <c r="Z90" s="24"/>
     </row>
-    <row r="91" ht="29.25" customHeight="1">
+    <row r="91" ht="18.75" customHeight="1">
       <c r="A91" s="40"/>
-      <c r="B91" s="50" t="s">
-        <v>55</v>
+      <c r="B91" s="63" t="s">
+        <v>62</v>
       </c>
-      <c r="C91" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="D91" s="47" t="s">
-        <v>63</v>
-      </c>
-      <c r="E91" s="57"/>
+      <c r="C91" s="19"/>
+      <c r="D91" s="19"/>
+      <c r="E91" s="20"/>
       <c r="F91" s="40"/>
       <c r="G91" s="49"/>
       <c r="H91" s="49"/>
@@ -5582,16 +5599,16 @@
       <c r="Y91" s="24"/>
       <c r="Z91" s="24"/>
     </row>
-    <row r="92" ht="21.0" customHeight="1">
+    <row r="92" ht="29.25" customHeight="1">
       <c r="A92" s="40"/>
       <c r="B92" s="50" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C92" s="50" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
-      <c r="D92" s="58" t="s">
-        <v>64</v>
+      <c r="D92" s="47" t="s">
+        <v>63</v>
       </c>
       <c r="E92" s="57"/>
       <c r="F92" s="40"/>
@@ -5618,16 +5635,16 @@
     </row>
     <row r="93" ht="21.0" customHeight="1">
       <c r="A93" s="40"/>
-      <c r="B93" s="64" t="s">
-        <v>65</v>
+      <c r="B93" s="50" t="s">
+        <v>58</v>
       </c>
-      <c r="C93" s="65" t="s">
-        <v>52</v>
+      <c r="C93" s="50" t="s">
+        <v>58</v>
       </c>
-      <c r="D93" s="66" t="s">
-        <v>66</v>
+      <c r="D93" s="58" t="s">
+        <v>64</v>
       </c>
-      <c r="E93" s="67"/>
+      <c r="E93" s="57"/>
       <c r="F93" s="40"/>
       <c r="G93" s="49"/>
       <c r="H93" s="49"/>
@@ -5650,14 +5667,18 @@
       <c r="Y93" s="24"/>
       <c r="Z93" s="24"/>
     </row>
-    <row r="94" ht="18.75" customHeight="1">
+    <row r="94" ht="21.0" customHeight="1">
       <c r="A94" s="40"/>
-      <c r="B94" s="68" t="s">
-        <v>67</v>
+      <c r="B94" s="64" t="s">
+        <v>65</v>
       </c>
-      <c r="C94" s="19"/>
-      <c r="D94" s="19"/>
-      <c r="E94" s="20"/>
+      <c r="C94" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="D94" s="66" t="s">
+        <v>66</v>
+      </c>
+      <c r="E94" s="67"/>
       <c r="F94" s="40"/>
       <c r="G94" s="49"/>
       <c r="H94" s="49"/>
@@ -5680,18 +5701,14 @@
       <c r="Y94" s="24"/>
       <c r="Z94" s="24"/>
     </row>
-    <row r="95" ht="29.25" customHeight="1">
+    <row r="95" ht="18.75" customHeight="1">
       <c r="A95" s="40"/>
-      <c r="B95" s="50" t="s">
-        <v>55</v>
+      <c r="B95" s="68" t="s">
+        <v>67</v>
       </c>
-      <c r="C95" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="D95" s="47" t="s">
-        <v>68</v>
-      </c>
-      <c r="E95" s="57"/>
+      <c r="C95" s="19"/>
+      <c r="D95" s="19"/>
+      <c r="E95" s="20"/>
       <c r="F95" s="40"/>
       <c r="G95" s="49"/>
       <c r="H95" s="49"/>
@@ -5714,16 +5731,16 @@
       <c r="Y95" s="24"/>
       <c r="Z95" s="24"/>
     </row>
-    <row r="96" ht="21.0" customHeight="1">
+    <row r="96" ht="29.25" customHeight="1">
       <c r="A96" s="40"/>
       <c r="B96" s="50" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C96" s="50" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
-      <c r="D96" s="58" t="s">
-        <v>69</v>
+      <c r="D96" s="47" t="s">
+        <v>68</v>
       </c>
       <c r="E96" s="57"/>
       <c r="F96" s="40"/>
@@ -5748,82 +5765,82 @@
       <c r="Y96" s="24"/>
       <c r="Z96" s="24"/>
     </row>
-    <row r="97" ht="16.5" customHeight="1">
-      <c r="A97" s="6"/>
-      <c r="B97" s="69" t="s">
-        <v>70</v>
+    <row r="97" ht="21.0" customHeight="1">
+      <c r="A97" s="40"/>
+      <c r="B97" s="50" t="s">
+        <v>58</v>
       </c>
-      <c r="C97" s="70" t="s">
-        <v>52</v>
+      <c r="C97" s="50" t="s">
+        <v>58</v>
       </c>
-      <c r="D97" s="71" t="s">
-        <v>71</v>
+      <c r="D97" s="58" t="s">
+        <v>69</v>
       </c>
-      <c r="E97" s="72"/>
+      <c r="E97" s="57"/>
       <c r="F97" s="40"/>
       <c r="G97" s="49"/>
       <c r="H97" s="49"/>
       <c r="I97" s="49"/>
       <c r="J97" s="49"/>
       <c r="K97" s="49"/>
-      <c r="L97" s="6"/>
-      <c r="M97" s="6"/>
-      <c r="N97" s="6"/>
-      <c r="O97" s="6"/>
-      <c r="P97" s="6"/>
-      <c r="Q97" s="6"/>
-      <c r="R97" s="6"/>
-      <c r="S97" s="6"/>
-      <c r="T97" s="6"/>
-      <c r="U97" s="6"/>
-      <c r="V97" s="6"/>
-      <c r="W97" s="6"/>
-      <c r="X97" s="6"/>
-      <c r="Y97" s="6"/>
-      <c r="Z97" s="6"/>
-    </row>
-    <row r="98" ht="18.75" customHeight="1">
-      <c r="A98" s="40"/>
-      <c r="B98" s="73" t="s">
-        <v>72</v>
+      <c r="L97" s="24"/>
+      <c r="M97" s="24"/>
+      <c r="N97" s="24"/>
+      <c r="O97" s="24"/>
+      <c r="P97" s="24"/>
+      <c r="Q97" s="24"/>
+      <c r="R97" s="24"/>
+      <c r="S97" s="24"/>
+      <c r="T97" s="24"/>
+      <c r="U97" s="24"/>
+      <c r="V97" s="24"/>
+      <c r="W97" s="24"/>
+      <c r="X97" s="24"/>
+      <c r="Y97" s="24"/>
+      <c r="Z97" s="24"/>
+    </row>
+    <row r="98" ht="16.5" customHeight="1">
+      <c r="A98" s="6"/>
+      <c r="B98" s="69" t="s">
+        <v>70</v>
       </c>
-      <c r="C98" s="19"/>
-      <c r="D98" s="19"/>
-      <c r="E98" s="20"/>
+      <c r="C98" s="70" t="s">
+        <v>52</v>
+      </c>
+      <c r="D98" s="71" t="s">
+        <v>71</v>
+      </c>
+      <c r="E98" s="72"/>
       <c r="F98" s="40"/>
       <c r="G98" s="49"/>
       <c r="H98" s="49"/>
       <c r="I98" s="49"/>
       <c r="J98" s="49"/>
       <c r="K98" s="49"/>
-      <c r="L98" s="24"/>
-      <c r="M98" s="24"/>
-      <c r="N98" s="24"/>
-      <c r="O98" s="24"/>
-      <c r="P98" s="24"/>
-      <c r="Q98" s="24"/>
-      <c r="R98" s="24"/>
-      <c r="S98" s="24"/>
-      <c r="T98" s="24"/>
-      <c r="U98" s="24"/>
-      <c r="V98" s="24"/>
-      <c r="W98" s="24"/>
-      <c r="X98" s="24"/>
-      <c r="Y98" s="24"/>
-      <c r="Z98" s="24"/>
-    </row>
-    <row r="99" ht="29.25" customHeight="1">
+      <c r="L98" s="6"/>
+      <c r="M98" s="6"/>
+      <c r="N98" s="6"/>
+      <c r="O98" s="6"/>
+      <c r="P98" s="6"/>
+      <c r="Q98" s="6"/>
+      <c r="R98" s="6"/>
+      <c r="S98" s="6"/>
+      <c r="T98" s="6"/>
+      <c r="U98" s="6"/>
+      <c r="V98" s="6"/>
+      <c r="W98" s="6"/>
+      <c r="X98" s="6"/>
+      <c r="Y98" s="6"/>
+      <c r="Z98" s="6"/>
+    </row>
+    <row r="99" ht="18.75" customHeight="1">
       <c r="A99" s="40"/>
-      <c r="B99" s="50" t="s">
-        <v>55</v>
+      <c r="B99" s="73" t="s">
+        <v>72</v>
       </c>
-      <c r="C99" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="D99" s="47" t="s">
-        <v>73</v>
-      </c>
-      <c r="E99" s="57"/>
+      <c r="C99" s="19"/>
+      <c r="D99" s="19"/>
+      <c r="E99" s="20"/>
       <c r="F99" s="40"/>
       <c r="G99" s="49"/>
       <c r="H99" s="49"/>
@@ -5846,16 +5863,16 @@
       <c r="Y99" s="24"/>
       <c r="Z99" s="24"/>
     </row>
-    <row r="100" ht="21.0" customHeight="1">
+    <row r="100" ht="29.25" customHeight="1">
       <c r="A100" s="40"/>
       <c r="B100" s="50" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C100" s="50" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
-      <c r="D100" s="58" t="s">
-        <v>74</v>
+      <c r="D100" s="47" t="s">
+        <v>73</v>
       </c>
       <c r="E100" s="57"/>
       <c r="F100" s="40"/>
@@ -5880,52 +5897,52 @@
       <c r="Y100" s="24"/>
       <c r="Z100" s="24"/>
     </row>
-    <row r="101" ht="16.5" customHeight="1">
-      <c r="A101" s="6"/>
-      <c r="B101" s="74" t="s">
-        <v>75</v>
+    <row r="101" ht="21.0" customHeight="1">
+      <c r="A101" s="40"/>
+      <c r="B101" s="50" t="s">
+        <v>58</v>
       </c>
-      <c r="C101" s="75" t="s">
-        <v>52</v>
+      <c r="C101" s="50" t="s">
+        <v>58</v>
       </c>
-      <c r="D101" s="76" t="s">
-        <v>76</v>
+      <c r="D101" s="58" t="s">
+        <v>74</v>
       </c>
-      <c r="E101" s="77"/>
+      <c r="E101" s="57"/>
       <c r="F101" s="40"/>
       <c r="G101" s="49"/>
       <c r="H101" s="49"/>
       <c r="I101" s="49"/>
       <c r="J101" s="49"/>
       <c r="K101" s="49"/>
-      <c r="L101" s="6"/>
-      <c r="M101" s="6"/>
-      <c r="N101" s="6"/>
-      <c r="O101" s="6"/>
-      <c r="P101" s="6"/>
-      <c r="Q101" s="6"/>
-      <c r="R101" s="6"/>
-      <c r="S101" s="6"/>
-      <c r="T101" s="6"/>
-      <c r="U101" s="6"/>
-      <c r="V101" s="6"/>
-      <c r="W101" s="6"/>
-      <c r="X101" s="6"/>
-      <c r="Y101" s="6"/>
-      <c r="Z101" s="6"/>
-    </row>
-    <row r="102" ht="33.75" customHeight="1">
+      <c r="L101" s="24"/>
+      <c r="M101" s="24"/>
+      <c r="N101" s="24"/>
+      <c r="O101" s="24"/>
+      <c r="P101" s="24"/>
+      <c r="Q101" s="24"/>
+      <c r="R101" s="24"/>
+      <c r="S101" s="24"/>
+      <c r="T101" s="24"/>
+      <c r="U101" s="24"/>
+      <c r="V101" s="24"/>
+      <c r="W101" s="24"/>
+      <c r="X101" s="24"/>
+      <c r="Y101" s="24"/>
+      <c r="Z101" s="24"/>
+    </row>
+    <row r="102" ht="16.5" customHeight="1">
       <c r="A102" s="6"/>
-      <c r="B102" s="50" t="s">
-        <v>55</v>
+      <c r="B102" s="74" t="s">
+        <v>75</v>
       </c>
-      <c r="C102" s="37" t="s">
-        <v>77</v>
+      <c r="C102" s="75" t="s">
+        <v>52</v>
       </c>
-      <c r="D102" s="78" t="s">
-        <v>78</v>
+      <c r="D102" s="76" t="s">
+        <v>76</v>
       </c>
-      <c r="E102" s="79"/>
+      <c r="E102" s="77"/>
       <c r="F102" s="40"/>
       <c r="G102" s="49"/>
       <c r="H102" s="49"/>
@@ -5948,18 +5965,18 @@
       <c r="Y102" s="6"/>
       <c r="Z102" s="6"/>
     </row>
-    <row r="103" ht="16.5" customHeight="1">
+    <row r="103" ht="33.75" customHeight="1">
       <c r="A103" s="6"/>
-      <c r="B103" s="80" t="s">
-        <v>79</v>
+      <c r="B103" s="50" t="s">
+        <v>55</v>
       </c>
-      <c r="C103" s="81" t="s">
-        <v>52</v>
+      <c r="C103" s="37" t="s">
+        <v>77</v>
       </c>
-      <c r="D103" s="82" t="s">
-        <v>80</v>
+      <c r="D103" s="78" t="s">
+        <v>78</v>
       </c>
-      <c r="E103" s="83"/>
+      <c r="E103" s="79"/>
       <c r="F103" s="40"/>
       <c r="G103" s="49"/>
       <c r="H103" s="49"/>
@@ -5982,20 +5999,18 @@
       <c r="Y103" s="6"/>
       <c r="Z103" s="6"/>
     </row>
-    <row r="104" ht="54.0" customHeight="1">
+    <row r="104" ht="16.5" customHeight="1">
       <c r="A104" s="6"/>
-      <c r="B104" s="50" t="s">
-        <v>81</v>
+      <c r="B104" s="80" t="s">
+        <v>79</v>
       </c>
-      <c r="C104" s="37" t="s">
-        <v>77</v>
+      <c r="C104" s="81" t="s">
+        <v>52</v>
       </c>
-      <c r="D104" s="78" t="s">
-        <v>82</v>
+      <c r="D104" s="82" t="s">
+        <v>80</v>
       </c>
-      <c r="E104" s="84">
-        <v>2958101.0</v>
-      </c>
+      <c r="E104" s="83"/>
       <c r="F104" s="40"/>
       <c r="G104" s="49"/>
       <c r="H104" s="49"/>
@@ -6018,16 +6033,20 @@
       <c r="Y104" s="6"/>
       <c r="Z104" s="6"/>
     </row>
-    <row r="105" ht="16.5" customHeight="1">
+    <row r="105" ht="54.0" customHeight="1">
       <c r="A105" s="6"/>
       <c r="B105" s="50" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C105" s="37" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
-      <c r="D105" s="78"/>
-      <c r="E105" s="85"/>
+      <c r="D105" s="78" t="s">
+        <v>82</v>
+      </c>
+      <c r="E105" s="84">
+        <v>2958101.0</v>
+      </c>
       <c r="F105" s="40"/>
       <c r="G105" s="49"/>
       <c r="H105" s="49"/>
@@ -6050,20 +6069,16 @@
       <c r="Y105" s="6"/>
       <c r="Z105" s="6"/>
     </row>
-    <row r="106" ht="48.0" customHeight="1">
+    <row r="106" ht="16.5" customHeight="1">
       <c r="A106" s="6"/>
       <c r="B106" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C106" s="37" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
-      <c r="D106" s="78" t="s">
-        <v>85</v>
-      </c>
-      <c r="E106" s="84">
-        <v>2958101.0</v>
-      </c>
+      <c r="D106" s="78"/>
+      <c r="E106" s="85"/>
       <c r="F106" s="40"/>
       <c r="G106" s="49"/>
       <c r="H106" s="49"/>
@@ -6086,18 +6101,20 @@
       <c r="Y106" s="6"/>
       <c r="Z106" s="6"/>
     </row>
-    <row r="107" ht="34.5" customHeight="1">
+    <row r="107" ht="48.0" customHeight="1">
       <c r="A107" s="6"/>
-      <c r="B107" s="86" t="s">
-        <v>86</v>
+      <c r="B107" s="50" t="s">
+        <v>84</v>
       </c>
-      <c r="C107" s="87" t="s">
-        <v>58</v>
+      <c r="C107" s="37" t="s">
+        <v>77</v>
       </c>
-      <c r="D107" s="88" t="s">
-        <v>87</v>
+      <c r="D107" s="78" t="s">
+        <v>85</v>
       </c>
-      <c r="E107" s="88"/>
+      <c r="E107" s="84">
+        <v>2958101.0</v>
+      </c>
       <c r="F107" s="40"/>
       <c r="G107" s="49"/>
       <c r="H107" s="49"/>
@@ -6120,18 +6137,18 @@
       <c r="Y107" s="6"/>
       <c r="Z107" s="6"/>
     </row>
-    <row r="108" ht="51.0" customHeight="1">
+    <row r="108" ht="34.5" customHeight="1">
       <c r="A108" s="6"/>
-      <c r="B108" s="50" t="s">
-        <v>88</v>
+      <c r="B108" s="86" t="s">
+        <v>86</v>
       </c>
-      <c r="C108" s="41" t="s">
-        <v>50</v>
+      <c r="C108" s="87" t="s">
+        <v>58</v>
       </c>
-      <c r="D108" s="47" t="s">
-        <v>33</v>
+      <c r="D108" s="88" t="s">
+        <v>87</v>
       </c>
-      <c r="E108" s="85"/>
+      <c r="E108" s="88"/>
       <c r="F108" s="40"/>
       <c r="G108" s="49"/>
       <c r="H108" s="49"/>
@@ -6154,16 +6171,16 @@
       <c r="Y108" s="6"/>
       <c r="Z108" s="6"/>
     </row>
-    <row r="109" ht="48.0" customHeight="1">
+    <row r="109" ht="51.0" customHeight="1">
       <c r="A109" s="6"/>
       <c r="B109" s="50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C109" s="41" t="s">
         <v>50</v>
       </c>
       <c r="D109" s="47" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E109" s="85"/>
       <c r="F109" s="40"/>
@@ -6188,18 +6205,24 @@
       <c r="Y109" s="6"/>
       <c r="Z109" s="6"/>
     </row>
-    <row r="110" ht="16.5" customHeight="1">
+    <row r="110" ht="48.0" customHeight="1">
       <c r="A110" s="6"/>
-      <c r="B110" s="6"/>
-      <c r="C110" s="6"/>
-      <c r="D110" s="6"/>
-      <c r="E110" s="6"/>
-      <c r="F110" s="6"/>
-      <c r="G110" s="6"/>
-      <c r="H110" s="6"/>
-      <c r="I110" s="6"/>
-      <c r="J110" s="6"/>
-      <c r="K110" s="6"/>
+      <c r="B110" s="50" t="s">
+        <v>89</v>
+      </c>
+      <c r="C110" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="D110" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="E110" s="85"/>
+      <c r="F110" s="40"/>
+      <c r="G110" s="49"/>
+      <c r="H110" s="49"/>
+      <c r="I110" s="49"/>
+      <c r="J110" s="49"/>
+      <c r="K110" s="49"/>
       <c r="L110" s="6"/>
       <c r="M110" s="6"/>
       <c r="N110" s="6"/>
@@ -30184,13 +30207,41 @@
       <c r="Y966" s="6"/>
       <c r="Z966" s="6"/>
     </row>
+    <row r="967" ht="16.5" customHeight="1">
+      <c r="A967" s="6"/>
+      <c r="B967" s="6"/>
+      <c r="C967" s="6"/>
+      <c r="D967" s="6"/>
+      <c r="E967" s="6"/>
+      <c r="F967" s="6"/>
+      <c r="G967" s="6"/>
+      <c r="H967" s="6"/>
+      <c r="I967" s="6"/>
+      <c r="J967" s="6"/>
+      <c r="K967" s="6"/>
+      <c r="L967" s="6"/>
+      <c r="M967" s="6"/>
+      <c r="N967" s="6"/>
+      <c r="O967" s="6"/>
+      <c r="P967" s="6"/>
+      <c r="Q967" s="6"/>
+      <c r="R967" s="6"/>
+      <c r="S967" s="6"/>
+      <c r="T967" s="6"/>
+      <c r="U967" s="6"/>
+      <c r="V967" s="6"/>
+      <c r="W967" s="6"/>
+      <c r="X967" s="6"/>
+      <c r="Y967" s="6"/>
+      <c r="Z967" s="6"/>
+    </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="C80:D80"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="B90:E90"/>
-    <mergeCell ref="B94:E94"/>
-    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B95:E95"/>
+    <mergeCell ref="B99:E99"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="E1:I1"/>
     <mergeCell ref="B64:H66"/>
@@ -30338,10 +30389,10 @@
         <v>9</v>
       </c>
       <c r="C5" s="91" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" s="92" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E5" s="20"/>
       <c r="F5" s="90"/>
@@ -52277,17 +52328,175 @@
       <c r="O39" s="104"/>
     </row>
     <row r="40">
-      <c r="L40" s="122" t="s">
+      <c r="L40" s="105" t="s">
         <v>91</v>
       </c>
-      <c r="M40" s="123"/>
-      <c r="N40" s="123"/>
-      <c r="O40" s="124"/>
+      <c r="O40" s="104"/>
+    </row>
+    <row r="41">
+      <c r="L41" s="105" t="s">
+        <v>92</v>
+      </c>
+      <c r="O41" s="104"/>
+    </row>
+    <row r="42">
+      <c r="L42" s="105" t="s">
+        <v>93</v>
+      </c>
+      <c r="O42" s="104"/>
+    </row>
+    <row r="43">
+      <c r="L43" s="103"/>
+      <c r="O43" s="104"/>
+    </row>
+    <row r="44">
+      <c r="L44" s="106" t="s">
+        <v>75</v>
+      </c>
+      <c r="M44" s="19"/>
+      <c r="N44" s="19"/>
+      <c r="O44" s="20"/>
+    </row>
+    <row r="45">
+      <c r="L45" s="107"/>
+      <c r="M45" s="108"/>
+      <c r="N45" s="108"/>
+      <c r="O45" s="109"/>
+    </row>
+    <row r="46">
+      <c r="L46" s="110" t="s">
+        <v>94</v>
+      </c>
+      <c r="M46" s="111" t="s">
+        <v>95</v>
+      </c>
+      <c r="N46" s="112" t="s">
+        <v>96</v>
+      </c>
+      <c r="O46" s="109"/>
+    </row>
+    <row r="47">
+      <c r="L47" s="107"/>
+      <c r="M47" s="108"/>
+      <c r="N47" s="108"/>
+      <c r="O47" s="109"/>
+    </row>
+    <row r="48">
+      <c r="L48" s="114" t="s">
+        <v>79</v>
+      </c>
+      <c r="M48" s="19"/>
+      <c r="N48" s="19"/>
+      <c r="O48" s="20"/>
+    </row>
+    <row r="49">
+      <c r="L49" s="105"/>
+      <c r="O49" s="104"/>
+    </row>
+    <row r="50">
+      <c r="L50" s="105"/>
+      <c r="M50" s="111" t="s">
+        <v>95</v>
+      </c>
+      <c r="N50" s="115" t="s">
+        <v>100</v>
+      </c>
+      <c r="O50" s="109"/>
+    </row>
+    <row r="51">
+      <c r="L51" s="105"/>
+      <c r="M51" s="116" t="s">
+        <v>102</v>
+      </c>
+      <c r="N51" s="117" t="s">
+        <v>103</v>
+      </c>
+      <c r="O51" s="104"/>
+    </row>
+    <row r="52">
+      <c r="L52" s="105"/>
+      <c r="M52" s="111" t="s">
+        <v>95</v>
+      </c>
+      <c r="N52" s="115" t="s">
+        <v>100</v>
+      </c>
+      <c r="O52" s="109"/>
+    </row>
+    <row r="53">
+      <c r="L53" s="105"/>
+      <c r="N53" s="117" t="s">
+        <v>103</v>
+      </c>
+      <c r="O53" s="104"/>
+    </row>
+    <row r="54">
+      <c r="L54" s="105"/>
+      <c r="O54" s="109"/>
+    </row>
+    <row r="55">
+      <c r="L55" s="119" t="s">
+        <v>106</v>
+      </c>
+      <c r="M55" s="19"/>
+      <c r="N55" s="19"/>
+      <c r="O55" s="20"/>
+    </row>
+    <row r="56">
+      <c r="L56" s="105"/>
+      <c r="O56" s="104"/>
+    </row>
+    <row r="57">
+      <c r="L57" s="105"/>
+      <c r="M57" s="120" t="s">
+        <v>49</v>
+      </c>
+      <c r="N57" s="3"/>
+      <c r="O57" s="104"/>
+    </row>
+    <row r="58">
+      <c r="L58" s="105"/>
+      <c r="M58" s="7"/>
+      <c r="N58" s="9"/>
+      <c r="O58" s="104"/>
+    </row>
+    <row r="59">
+      <c r="L59" s="105"/>
+      <c r="O59" s="104"/>
+    </row>
+    <row r="60">
+      <c r="L60" s="105"/>
+      <c r="M60" s="121" t="s">
+        <v>89</v>
+      </c>
+      <c r="N60" s="3"/>
+      <c r="O60" s="104"/>
+    </row>
+    <row r="61">
+      <c r="L61" s="105"/>
+      <c r="M61" s="7"/>
+      <c r="N61" s="9"/>
+      <c r="O61" s="104"/>
+    </row>
+    <row r="62">
+      <c r="L62" s="103"/>
+      <c r="O62" s="104"/>
+    </row>
+    <row r="63">
+      <c r="L63" s="122"/>
+      <c r="M63" s="123"/>
+      <c r="N63" s="123"/>
+      <c r="O63" s="124"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="14">
     <mergeCell ref="L26:O26"/>
     <mergeCell ref="L37:O37"/>
+    <mergeCell ref="L44:O44"/>
+    <mergeCell ref="L48:O48"/>
+    <mergeCell ref="L55:O55"/>
+    <mergeCell ref="M57:N58"/>
+    <mergeCell ref="M60:N61"/>
     <mergeCell ref="Q6:T6"/>
     <mergeCell ref="L9:O9"/>
     <mergeCell ref="Q10:T10"/>
